--- a/output/full_scan/batch_seq1_2026-07-16.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-16.xlsx
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>210.0006183081474</v>
+        <v>210.0006183081473</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>46</v>
